--- a/BVSimulationFiles/31.xlsx
+++ b/BVSimulationFiles/31.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1 Copy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -414,75 +414,72 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.00035</v>
+        <v>0.0003652173913043478</v>
       </c>
       <c r="D1" t="n">
-        <v>0.0007</v>
+        <v>0.0007304347826086956</v>
       </c>
       <c r="E1" t="n">
-        <v>0.00105</v>
+        <v>0.001095652173913043</v>
       </c>
       <c r="F1" t="n">
-        <v>0.0014</v>
+        <v>0.001460869565217391</v>
       </c>
       <c r="G1" t="n">
-        <v>0.00175</v>
+        <v>0.001826086956521739</v>
       </c>
       <c r="H1" t="n">
-        <v>0.0021</v>
+        <v>0.002191304347826087</v>
       </c>
       <c r="I1" t="n">
-        <v>0.00245</v>
+        <v>0.002556521739130435</v>
       </c>
       <c r="J1" t="n">
-        <v>0.0028</v>
+        <v>0.002921739130434782</v>
       </c>
       <c r="K1" t="n">
-        <v>0.00315</v>
+        <v>0.00328695652173913</v>
       </c>
       <c r="L1" t="n">
-        <v>0.0035</v>
+        <v>0.003652173913043478</v>
       </c>
       <c r="M1" t="n">
-        <v>0.00385</v>
+        <v>0.004017391304347826</v>
       </c>
       <c r="N1" t="n">
-        <v>0.0042</v>
+        <v>0.004382608695652174</v>
       </c>
       <c r="O1" t="n">
-        <v>0.00455</v>
+        <v>0.004747826086956521</v>
       </c>
       <c r="P1" t="n">
-        <v>0.0049</v>
+        <v>0.00511304347826087</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.00525</v>
+        <v>0.005478260869565217</v>
       </c>
       <c r="R1" t="n">
-        <v>0.0056</v>
+        <v>0.005843478260869565</v>
       </c>
       <c r="S1" t="n">
-        <v>0.00595</v>
+        <v>0.006208695652173912</v>
       </c>
       <c r="T1" t="n">
-        <v>0.0063</v>
+        <v>0.00657391304347826</v>
       </c>
       <c r="U1" t="n">
-        <v>0.00665</v>
+        <v>0.006939130434782608</v>
       </c>
       <c r="V1" t="n">
-        <v>0.007</v>
+        <v>0.007304347826086956</v>
       </c>
       <c r="W1" t="n">
-        <v>0.00735</v>
+        <v>0.007669565217391303</v>
       </c>
       <c r="X1" t="n">
-        <v>0.0077</v>
+        <v>0.008034782608695652</v>
       </c>
       <c r="Y1" t="n">
-        <v>0.00805</v>
-      </c>
-      <c r="Z1" t="n">
         <v>0.008399999999999999</v>
       </c>
     </row>
